--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/解析结果/预案草稿/2.设备配置信息.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/解析结果/预案草稿/2.设备配置信息.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CloudEngine 16800 V300</t>
+          <t>CloudEngine 16800 V200R020C10SPC800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CloudEngine 9800 V200R020C00</t>
+          <t>CloudEngine 9800 V200R025C00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Atlas 900 A3 SuperPoD 1.0.2</t>
+          <t>Atlas 900 A3 SuperPoD 1.0.T23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
